--- a/artfynd/A 28033-2023 artfynd.xlsx
+++ b/artfynd/A 28033-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28033-2023 artfynd.xlsx
+++ b/artfynd/A 28033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63845334</v>
+        <v>71053380</v>
       </c>
       <c r="B2" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,20 +703,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Natorp yta 3, Vstm</t>
+          <t>Natorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503321.8770364535</v>
+        <v>503336</v>
       </c>
       <c r="R2" t="n">
-        <v>6610210.713775321</v>
+        <v>6610229</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,66 +759,62 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-08-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Räkning av larvkolonier inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>2-3 kolonier på ung ask</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Jonas Örnborg, Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112820944</v>
+        <v>73792600</v>
       </c>
       <c r="B3" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,41 +822,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorp yta 3, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503356</v>
+        <v>503322</v>
       </c>
       <c r="R3" t="n">
-        <v>6610187</v>
+        <v>6610211</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,17 +890,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2018-07-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,27 +915,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112820950</v>
+        <v>105554654</v>
       </c>
       <c r="B4" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,38 +942,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503370</v>
+        <v>503377</v>
       </c>
       <c r="R4" t="n">
-        <v>6610173</v>
+        <v>6610185</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,17 +1005,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,11 +1026,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1014,19 +1053,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112820918</v>
+        <v>105554707</v>
       </c>
       <c r="B5" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,38 +1072,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503247</v>
+        <v>503381</v>
       </c>
       <c r="R5" t="n">
-        <v>6610235</v>
+        <v>6610202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,17 +1135,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,11 +1156,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1125,19 +1183,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112820987</v>
+        <v>105554708</v>
       </c>
       <c r="B6" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,38 +1202,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503296</v>
+        <v>503378</v>
       </c>
       <c r="R6" t="n">
-        <v>6610165</v>
+        <v>6610187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,17 +1265,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Från 0.3 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,11 +1286,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1236,19 +1313,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112820975</v>
+        <v>105554709</v>
       </c>
       <c r="B7" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,38 +1332,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503254</v>
+        <v>503387</v>
       </c>
       <c r="R7" t="n">
-        <v>6610139</v>
+        <v>6610172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,17 +1395,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,11 +1416,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1347,19 +1443,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112820953</v>
+        <v>105554714</v>
       </c>
       <c r="B8" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,38 +1462,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503365</v>
+        <v>503348</v>
       </c>
       <c r="R8" t="n">
-        <v>6610155</v>
+        <v>6610233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,17 +1525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Från 0.3 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,70 +1546,89 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112820972</v>
+        <v>105554717</v>
       </c>
       <c r="B9" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>100943</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503254</v>
+        <v>503334</v>
       </c>
       <c r="R9" t="n">
-        <v>6610141</v>
+        <v>6610231</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,12 +1655,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,31 +1676,45 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112820908</v>
+        <v>105554720</v>
       </c>
       <c r="B10" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,21 +1722,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1606,16 +1744,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:16 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503293</v>
+        <v>503329</v>
       </c>
       <c r="R10" t="n">
-        <v>6610265</v>
+        <v>6610261</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,17 +1785,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>8 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,11 +1806,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1675,19 +1833,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112820958</v>
+        <v>105554730</v>
       </c>
       <c r="B11" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,38 +1852,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:16 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503298</v>
+        <v>503338</v>
       </c>
       <c r="R11" t="n">
-        <v>6610146</v>
+        <v>6610247</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,17 +1915,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,31 +1936,45 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112820926</v>
+        <v>113473045</v>
       </c>
       <c r="B12" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,38 +1982,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503229</v>
+        <v>503376</v>
       </c>
       <c r="R12" t="n">
-        <v>6610216</v>
+        <v>6610193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,17 +2045,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 4 dm dbh. Över 15 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,31 +2061,45 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112820985</v>
+        <v>113473228</v>
       </c>
       <c r="B13" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,38 +2107,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503257</v>
+        <v>503348</v>
       </c>
       <c r="R13" t="n">
-        <v>6610182</v>
+        <v>6610236</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,17 +2170,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 0.3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,11 +2186,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2008,54 +2213,62 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112820978</v>
+        <v>113473564</v>
       </c>
       <c r="B14" t="n">
-        <v>99329</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>100943</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:3 Ömansttorp, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503241</v>
+        <v>503303</v>
       </c>
       <c r="R14" t="n">
-        <v>6610157</v>
+        <v>6610242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,12 +2295,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Larvstadie 2 dominerade.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,11 +2316,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2110,54 +2343,62 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112820966</v>
+        <v>113473649</v>
       </c>
       <c r="B15" t="n">
-        <v>99418</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100943</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503281</v>
+        <v>503386</v>
       </c>
       <c r="R15" t="n">
-        <v>6610146</v>
+        <v>6610200</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,12 +2425,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,31 +2441,45 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112820901</v>
+        <v>120766169</v>
       </c>
       <c r="B16" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,21 +2487,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2254,16 +2509,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503299</v>
+        <v>503366</v>
       </c>
       <c r="R16" t="n">
-        <v>6610247</v>
+        <v>6610192</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,17 +2555,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Träd 2 dm dbh. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,11 +2571,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2323,19 +2598,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112820900</v>
+        <v>120766170</v>
       </c>
       <c r="B17" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,38 +2617,48 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503297</v>
+        <v>503381</v>
       </c>
       <c r="R17" t="n">
-        <v>6610235</v>
+        <v>6610176</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,17 +2685,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 till 4 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,11 +2701,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2434,19 +2728,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112820964</v>
+        <v>120766171</v>
       </c>
       <c r="B18" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,38 +2747,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503285</v>
+        <v>503375</v>
       </c>
       <c r="R18" t="n">
-        <v>6610146</v>
+        <v>6610180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,17 +2815,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Från ca 8 till 30 cm dbh och från ca 15 till 20 m höga. Några döende av askskottsjuka andra tillsynes helt friska. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,11 +2831,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2545,19 +2858,18 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112820969</v>
+        <v>129833433</v>
       </c>
       <c r="B19" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2565,38 +2877,48 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503262</v>
+        <v>503381</v>
       </c>
       <c r="R19" t="n">
-        <v>6610165</v>
+        <v>6610187</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,17 +2945,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,66 +2961,94 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112820940</v>
+        <v>129833434</v>
       </c>
       <c r="B20" t="n">
-        <v>99329</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>100943</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503305</v>
+        <v>503376</v>
       </c>
       <c r="R20" t="n">
-        <v>6610238</v>
+        <v>6610192</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,17 +3075,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Förekommer åtminstone i norra delen av beståndet.</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2751,53 +3091,67 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112820981</v>
+        <v>129833435</v>
       </c>
       <c r="B21" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>100943</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2805,16 +3159,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503277</v>
+        <v>503333</v>
       </c>
       <c r="R21" t="n">
-        <v>6610179</v>
+        <v>6610228</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2841,12 +3205,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,70 +3221,94 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112820943</v>
+        <v>129833466</v>
       </c>
       <c r="B22" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222412</v>
+        <v>100943</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503341</v>
+        <v>503372</v>
       </c>
       <c r="R22" t="n">
-        <v>6610198</v>
+        <v>6610213</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2947,12 +3335,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,11 +3351,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2975,54 +3378,67 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112820928</v>
+        <v>129833467</v>
       </c>
       <c r="B23" t="n">
-        <v>101438</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>225046</v>
+        <v>100943</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503234</v>
+        <v>503330</v>
       </c>
       <c r="R23" t="n">
-        <v>6610207</v>
+        <v>6610231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3049,17 +3465,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kring 1 m höga.</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,14 +3479,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3083,54 +3508,57 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112820938</v>
+        <v>112820900</v>
       </c>
       <c r="B24" t="n">
-        <v>99418</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>400 m SV Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503289</v>
+        <v>503297</v>
       </c>
       <c r="R24" t="n">
-        <v>6610251</v>
+        <v>6610235</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3167,7 +3595,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Vanlig i norra delen av beståndet.</t>
+          <t>2 till 4 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3194,15 +3622,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112820930</v>
+        <v>112820901</v>
       </c>
       <c r="B25" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,7 +3652,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3238,10 +3661,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503256</v>
+        <v>503299</v>
       </c>
       <c r="R25" t="n">
-        <v>6610210</v>
+        <v>6610247</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,7 +3701,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Träd 2 dm dbh. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3305,15 +3728,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112820967</v>
+        <v>112820903</v>
       </c>
       <c r="B26" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,7 +3758,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3349,10 +3767,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503280</v>
+        <v>503304</v>
       </c>
       <c r="R26" t="n">
-        <v>6610159</v>
+        <v>6610248</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3389,7 +3807,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 5 dm dbh. Ca 20 m hög. Spår av askskottsjuka. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2 till 5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3416,15 +3834,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112820914</v>
+        <v>112820904</v>
       </c>
       <c r="B27" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,7 +3864,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3460,7 +3873,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503237</v>
+        <v>503302</v>
       </c>
       <c r="R27" t="n">
         <v>6610265</v>
@@ -3500,7 +3913,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Över 15 m höga. 15 till 30 cm dbh. Minst tre med askskottsjuka. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>1 dm dbh och ca 8 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3527,32 +3940,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112820923</v>
+        <v>112820905</v>
       </c>
       <c r="B28" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3562,7 +3970,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3571,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503237</v>
+        <v>503303</v>
       </c>
       <c r="R28" t="n">
-        <v>6610228</v>
+        <v>6610262</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,6 +4015,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 till 3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3633,32 +4046,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112820906</v>
+        <v>112820907</v>
       </c>
       <c r="B29" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3668,7 +4076,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3677,10 +4085,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503287</v>
+        <v>503295</v>
       </c>
       <c r="R29" t="n">
-        <v>6610263</v>
+        <v>6610262</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3713,6 +4121,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Under 0.5 m höga plantor. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,15 +4152,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112820954</v>
+        <v>112820908</v>
       </c>
       <c r="B30" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,7 +4182,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3783,10 +4191,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503343</v>
+        <v>503294</v>
       </c>
       <c r="R30" t="n">
-        <v>6610144</v>
+        <v>6610265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,7 +4231,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ca 10 till 20 cm dbh och över 10 m höga. Ganska friska fortfarande. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>8 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3850,15 +4258,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112820931</v>
+        <v>112820909</v>
       </c>
       <c r="B31" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,7 +4288,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3894,10 +4297,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503266</v>
+        <v>503278</v>
       </c>
       <c r="R31" t="n">
-        <v>6610214</v>
+        <v>6610268</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,7 +4337,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3961,15 +4364,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112820925</v>
+        <v>112820910</v>
       </c>
       <c r="B32" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +4394,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4005,10 +4403,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503243</v>
+        <v>503278</v>
       </c>
       <c r="R32" t="n">
-        <v>6610208</v>
+        <v>6610274</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4045,7 +4443,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>4 till 8 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,15 +4470,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112820933</v>
+        <v>112820912</v>
       </c>
       <c r="B33" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4500,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4116,10 +4509,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503276</v>
+        <v>503254</v>
       </c>
       <c r="R33" t="n">
-        <v>6610240</v>
+        <v>6610261</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4156,7 +4549,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Från 1 till 3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4183,15 +4576,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112820952</v>
+        <v>112820913</v>
       </c>
       <c r="B34" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4218,7 +4606,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4227,10 +4615,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503371</v>
+        <v>503253</v>
       </c>
       <c r="R34" t="n">
-        <v>6610163</v>
+        <v>6610273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4267,7 +4655,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ca 15 till 30 cm dbh och över 10 m höga. Med askskottsjuka men levande. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>3 till 7 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4294,15 +4682,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112820917</v>
+        <v>112820914</v>
       </c>
       <c r="B35" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4329,7 +4712,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4338,10 +4721,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503266</v>
+        <v>503236</v>
       </c>
       <c r="R35" t="n">
-        <v>6610239</v>
+        <v>6610265</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,7 +4761,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Träd med tre stammar med vardera ca 2 dm dbh. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Över 15 m höga. 15 till 30 cm dbh. Minst tre med askskottsjuka. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4405,32 +4788,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112820962</v>
+        <v>112820915</v>
       </c>
       <c r="B36" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4440,7 +4818,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>300</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4449,10 +4827,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503294</v>
+        <v>503240</v>
       </c>
       <c r="R36" t="n">
-        <v>6610143</v>
+        <v>6610256</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,6 +4863,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4511,32 +4894,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112820927</v>
+        <v>112820916</v>
       </c>
       <c r="B37" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4546,7 +4924,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4555,10 +4933,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503229</v>
+        <v>503260</v>
       </c>
       <c r="R37" t="n">
-        <v>6610214</v>
+        <v>6610237</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4591,6 +4969,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Från 2 till 7 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4617,15 +5000,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112820957</v>
+        <v>112820917</v>
       </c>
       <c r="B38" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4661,10 +5039,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503313</v>
+        <v>503266</v>
       </c>
       <c r="R38" t="n">
-        <v>6610136</v>
+        <v>6610239</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4701,7 +5079,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ca 4 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Träd med tre stammar med vardera ca 2 dm dbh. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4728,32 +5106,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112820951</v>
+        <v>112820918</v>
       </c>
       <c r="B39" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4763,7 +5136,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4772,10 +5145,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503377</v>
+        <v>503247</v>
       </c>
       <c r="R39" t="n">
-        <v>6610162</v>
+        <v>6610235</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4812,7 +5185,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,15 +5212,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112820932</v>
+        <v>112820919</v>
       </c>
       <c r="B40" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4874,7 +5242,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4883,10 +5251,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503277</v>
+        <v>503232</v>
       </c>
       <c r="R40" t="n">
-        <v>6610236</v>
+        <v>6610241</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4923,7 +5291,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Kring 5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4950,32 +5318,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112820968</v>
+        <v>112820920</v>
       </c>
       <c r="B41" t="n">
-        <v>99329</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4985,27 +5348,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>400 m SV Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503272</v>
+        <v>503224</v>
       </c>
       <c r="R41" t="n">
-        <v>6610165</v>
+        <v>6610265</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5040,13 +5395,17 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Från 1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5065,15 +5424,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112820903</v>
+        <v>112820924</v>
       </c>
       <c r="B42" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,7 +5454,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5109,10 +5463,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503304</v>
+        <v>503237</v>
       </c>
       <c r="R42" t="n">
-        <v>6610249</v>
+        <v>6610228</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5149,7 +5503,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2 till 5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5176,15 +5530,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112820980</v>
+        <v>112820925</v>
       </c>
       <c r="B43" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5211,7 +5560,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5220,10 +5569,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503271</v>
+        <v>503243</v>
       </c>
       <c r="R43" t="n">
-        <v>6610184</v>
+        <v>6610208</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5260,7 +5609,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ca 15 cm dbh och över 18 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5287,15 +5636,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112820916</v>
+        <v>112820926</v>
       </c>
       <c r="B44" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5322,7 +5666,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5331,10 +5675,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503260</v>
+        <v>503229</v>
       </c>
       <c r="R44" t="n">
-        <v>6610237</v>
+        <v>6610215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5371,7 +5715,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Från 2 till 7 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 4 dm dbh. Över 15 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5398,32 +5742,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112820963</v>
+        <v>112820930</v>
       </c>
       <c r="B45" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5433,7 +5772,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5442,10 +5781,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503284</v>
+        <v>503256</v>
       </c>
       <c r="R45" t="n">
-        <v>6610144</v>
+        <v>6610210</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,6 +5817,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5504,32 +5848,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112820970</v>
+        <v>112820931</v>
       </c>
       <c r="B46" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5539,7 +5878,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5548,10 +5887,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503263</v>
+        <v>503266</v>
       </c>
       <c r="R46" t="n">
-        <v>6610161</v>
+        <v>6610214</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5584,6 +5923,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5610,38 +5954,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112820986</v>
+        <v>112820932</v>
       </c>
       <c r="B47" t="n">
-        <v>101438</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5650,10 +5993,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503299</v>
+        <v>503277</v>
       </c>
       <c r="R47" t="n">
-        <v>6610170</v>
+        <v>6610236</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5690,7 +6033,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Drygt 1 m hög.</t>
+          <t>Kring 5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5699,7 +6042,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5718,15 +6060,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112820983</v>
+        <v>112820933</v>
       </c>
       <c r="B48" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5753,7 +6090,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5762,10 +6099,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503253</v>
+        <v>503276</v>
       </c>
       <c r="R48" t="n">
-        <v>6610191</v>
+        <v>6610240</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5802,7 +6139,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ca 25 cm dbh och över 18 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 1 till 3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5829,15 +6166,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112820965</v>
+        <v>112820944</v>
       </c>
       <c r="B49" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5873,10 +6205,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503282</v>
+        <v>503357</v>
       </c>
       <c r="R49" t="n">
-        <v>6610142</v>
+        <v>6610187</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5913,7 +6245,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5940,15 +6272,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112820982</v>
+        <v>112820950</v>
       </c>
       <c r="B50" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5975,7 +6302,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5984,10 +6311,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503266</v>
+        <v>503370</v>
       </c>
       <c r="R50" t="n">
-        <v>6610189</v>
+        <v>6610173</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6024,7 +6351,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ca 15 cm dbh och över 15 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6051,32 +6378,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112820956</v>
+        <v>112820952</v>
       </c>
       <c r="B51" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6086,7 +6408,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6095,10 +6417,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503324</v>
+        <v>503371</v>
       </c>
       <c r="R51" t="n">
-        <v>6610131</v>
+        <v>6610163</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6131,6 +6453,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ca 15 till 30 cm dbh och över 10 m höga. Med askskottsjuka men levande. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6157,15 +6484,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112820924</v>
+        <v>112820953</v>
       </c>
       <c r="B52" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6192,7 +6514,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6201,10 +6523,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503237</v>
+        <v>503365</v>
       </c>
       <c r="R52" t="n">
-        <v>6610228</v>
+        <v>6610155</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6241,7 +6563,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.3 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6268,15 +6590,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112820912</v>
+        <v>112820954</v>
       </c>
       <c r="B53" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6303,7 +6620,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6312,10 +6629,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503253</v>
+        <v>503343</v>
       </c>
       <c r="R53" t="n">
-        <v>6610261</v>
+        <v>6610144</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6352,7 +6669,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 10 till 20 cm dbh och över 10 m höga. Ganska friska fortfarande. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6379,15 +6696,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112820979</v>
+        <v>112820957</v>
       </c>
       <c r="B54" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6414,7 +6726,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6423,10 +6735,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503243</v>
+        <v>503313</v>
       </c>
       <c r="R54" t="n">
-        <v>6610159</v>
+        <v>6610137</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6463,7 +6775,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 4 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6490,32 +6802,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112820945</v>
+        <v>112820958</v>
       </c>
       <c r="B55" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6525,7 +6832,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6534,10 +6841,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503365</v>
+        <v>503298</v>
       </c>
       <c r="R55" t="n">
-        <v>6610181</v>
+        <v>6610146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6570,6 +6877,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6596,32 +6908,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112820977</v>
+        <v>112820964</v>
       </c>
       <c r="B56" t="n">
-        <v>102635</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6631,7 +6938,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6640,10 +6947,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503245</v>
+        <v>503285</v>
       </c>
       <c r="R56" t="n">
-        <v>6610159</v>
+        <v>6610146</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6676,6 +6983,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Från ca 8 till 30 cm dbh och från ca 15 till 20 m höga. Några döende av askskottsjuka andra tillsynes helt friska. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6702,15 +7014,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112820907</v>
+        <v>112820965</v>
       </c>
       <c r="B57" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6737,7 +7044,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6746,10 +7053,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503294</v>
+        <v>503282</v>
       </c>
       <c r="R57" t="n">
-        <v>6610261</v>
+        <v>6610142</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6786,7 +7093,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Under 0.5 m höga plantor. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6813,15 +7120,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112820915</v>
+        <v>112820967</v>
       </c>
       <c r="B58" t="n">
-        <v>104776</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6848,7 +7150,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6857,10 +7159,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503240</v>
+        <v>503280</v>
       </c>
       <c r="R58" t="n">
-        <v>6610257</v>
+        <v>6610159</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6897,7 +7199,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 5 dm dbh. Ca 20 m hög. Spår av askskottsjuka. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6924,15 +7226,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113473564</v>
+        <v>112820969</v>
       </c>
       <c r="B59" t="n">
-        <v>42896</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6940,43 +7237,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>kolonier</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Natorpsområdet Yta 7:3 Ömansttorp, Vstm</t>
+          <t>400 m SV Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503303</v>
+        <v>503262</v>
       </c>
       <c r="R59" t="n">
-        <v>6610242</v>
+        <v>6610165</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7003,17 +7295,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Larvstadie 2 dominerade.</t>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7024,26 +7316,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -7051,11 +7328,3084 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>112820975</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>503254</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6610139</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>112820979</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>503243</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6610159</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>112820980</v>
+      </c>
+      <c r="B62" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>503271</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6610184</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ca 15 cm dbh och över 18 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>112820982</v>
+      </c>
+      <c r="B63" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>503266</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6610189</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ca 15 cm dbh och över 15 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>112820983</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>503253</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6610191</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ca 25 cm dbh och över 18 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>112820985</v>
+      </c>
+      <c r="B65" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>503256</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6610182</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>112820987</v>
+      </c>
+      <c r="B66" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>503296</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6610165</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Från 0.3 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>112820906</v>
+      </c>
+      <c r="B67" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>503288</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6610263</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>112820921</v>
+      </c>
+      <c r="B68" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>503221</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6610243</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>112820922</v>
+      </c>
+      <c r="B69" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>503228</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6610241</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>112820923</v>
+      </c>
+      <c r="B70" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>503237</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6610228</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>112820927</v>
+      </c>
+      <c r="B71" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>503229</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6610213</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>112820943</v>
+      </c>
+      <c r="B72" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>503341</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6610198</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>112820945</v>
+      </c>
+      <c r="B73" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>503365</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6610181</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>112820951</v>
+      </c>
+      <c r="B74" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>503377</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6610162</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>112820955</v>
+      </c>
+      <c r="B75" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>503329</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6610130</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>112820956</v>
+      </c>
+      <c r="B76" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>503324</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6610131</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>112820962</v>
+      </c>
+      <c r="B77" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>503294</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6610143</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>112820963</v>
+      </c>
+      <c r="B78" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>503284</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6610144</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>112820970</v>
+      </c>
+      <c r="B79" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>503263</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6610161</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>112820972</v>
+      </c>
+      <c r="B80" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>503254</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6610141</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>112820977</v>
+      </c>
+      <c r="B81" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>503245</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6610159</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>112820981</v>
+      </c>
+      <c r="B82" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>503278</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6610179</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>112820938</v>
+      </c>
+      <c r="B83" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>503290</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6610251</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Vanlig i norra delen av beståndet.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>112820966</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>503281</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6610146</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>112820940</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>503305</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6610237</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Förekommer åtminstone i norra delen av beståndet.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>112820968</v>
+      </c>
+      <c r="B86" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>503271</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6610165</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>112820978</v>
+      </c>
+      <c r="B87" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>503241</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6610157</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>112820928</v>
+      </c>
+      <c r="B88" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>503234</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6610206</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Kring 1 m höga.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>112820986</v>
+      </c>
+      <c r="B89" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>503299</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6610170</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Drygt 1 m hög.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28033-2023 artfynd.xlsx
+++ b/artfynd/A 28033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71053380</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73792600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1058,6 +1073,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554654</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1188,6 +1208,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554707</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1318,6 +1343,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554708</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1448,6 +1478,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554709</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1578,6 +1613,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1708,6 +1748,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554717</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1838,6 +1883,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554720</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1968,6 +2018,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554730</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2093,6 +2148,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473045</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2218,6 +2278,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473228</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2348,6 +2413,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473564</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2473,6 +2543,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473649</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2603,6 +2678,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766169</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2733,6 +2813,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766170</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2863,6 +2948,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766171</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2993,6 +3083,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833433</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3123,6 +3218,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833434</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3253,6 +3353,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833435</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3383,6 +3488,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833466</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3513,6 +3623,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833467</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3619,6 +3734,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820900</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3725,6 +3845,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820901</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3831,6 +3956,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820903</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3937,6 +4067,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820904</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4043,6 +4178,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820905</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4149,6 +4289,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820907</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4255,6 +4400,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820908</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4361,6 +4511,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820909</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4467,6 +4622,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820910</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4573,6 +4733,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820912</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4679,6 +4844,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820913</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4785,6 +4955,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820914</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4891,6 +5066,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820915</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4997,6 +5177,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820916</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5103,6 +5288,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820917</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5209,6 +5399,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820918</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5315,6 +5510,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820919</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5421,6 +5621,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820920</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5527,6 +5732,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820924</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5633,6 +5843,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820925</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5739,6 +5954,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820926</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5845,6 +6065,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820930</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5951,6 +6176,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820931</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6057,6 +6287,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820932</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6163,6 +6398,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820933</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6269,6 +6509,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820944</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6375,6 +6620,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820950</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6481,6 +6731,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820952</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6587,6 +6842,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820953</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6693,6 +6953,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820954</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6799,6 +7064,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820957</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6905,6 +7175,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820958</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7011,6 +7286,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820964</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7117,6 +7397,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820965</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7223,6 +7508,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820967</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7329,6 +7619,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820969</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7435,6 +7730,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820975</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7541,6 +7841,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820979</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7647,6 +7952,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820980</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7753,6 +8063,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820982</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7859,6 +8174,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820983</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7965,6 +8285,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820985</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8071,6 +8396,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820987</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8172,6 +8502,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820906</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8273,6 +8608,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820921</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8374,6 +8714,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820922</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8475,6 +8820,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820923</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8576,6 +8926,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820927</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8677,6 +9032,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820943</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8778,6 +9138,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820945</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8884,6 +9249,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820951</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8985,6 +9355,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820955</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9086,6 +9461,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820956</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9187,6 +9567,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820962</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9288,6 +9673,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820963</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9389,6 +9779,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820970</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9490,6 +9885,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820972</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9591,6 +9991,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820977</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9692,6 +10097,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820981</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9794,6 +10204,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820938</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9891,6 +10306,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820966</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9993,6 +10413,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820940</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10103,6 +10528,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820968</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10200,6 +10630,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820978</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10303,6 +10738,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820928</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10406,8 +10846,103 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820986</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>